--- a/04_Figures/F06_prediction/modules/T3/enet/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T3/enet/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,22 +146,25 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_red</t>
+    <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
     <t xml:space="preserve">ME_brown</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_yellow</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_green</t>
+    <t xml:space="preserve">ME_magenta</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_purple</t>
   </si>
   <si>
     <t xml:space="preserve">ME_black</t>
@@ -170,19 +173,10 @@
     <t xml:space="preserve">ME_greenyellow</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_magenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_pink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
+    <t xml:space="preserve">ME_red</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_yellow</t>
   </si>
 </sst>
 </file>
@@ -569,16 +563,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.206065030847899</v>
+        <v>-0.310435887866472</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.585714285714286</v>
+        <v>-0.567857142857143</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -602,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.206065030847899</v>
+        <v>-0.310435887866472</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.585714285714286</v>
+        <v>-0.567857142857143</v>
       </c>
       <c r="J3" t="n">
-        <v>0.592039800995025</v>
+        <v>0.711442786069652</v>
       </c>
       <c r="K3" t="n">
-        <v>0.154228855721393</v>
+        <v>0.0945273631840796</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.533086738874587</v>
+        <v>-1.91030015415649</v>
       </c>
       <c r="M3" t="n">
-        <v>1.40948578696501</v>
+        <v>9.62469104637227</v>
       </c>
     </row>
     <row r="4">
@@ -643,13 +637,13 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.471586971941869</v>
+        <v>-0.583560174560017</v>
       </c>
       <c r="I4" t="n">
         <v>-0.925</v>
@@ -676,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.471586971941869</v>
+        <v>-0.583560174560017</v>
       </c>
       <c r="I5" t="n">
         <v>-0.925</v>
       </c>
       <c r="J5" t="n">
-        <v>0.786069651741294</v>
+        <v>0.865671641791045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.278606965174129</v>
+        <v>0.318407960199005</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.538160257136139</v>
+        <v>-2.10696017739556</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1384352354464</v>
+        <v>9.43583592438207</v>
       </c>
     </row>
     <row r="6">
@@ -717,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.166987015861139</v>
+        <v>-0.923316097495398</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-0.964285714285714</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -750,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.166987015861139</v>
+        <v>-0.923316097495398</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>-0.964285714285714</v>
       </c>
       <c r="J7" t="n">
-        <v>0.512437810945274</v>
+        <v>0.930348258706468</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.303482587064677</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.633501140023073</v>
+        <v>-1.33425311659201</v>
       </c>
       <c r="M7" t="n">
-        <v>2.39399644580863</v>
+        <v>6.23503384725507</v>
       </c>
     </row>
     <row r="8">
@@ -791,13 +785,13 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.215067169109523</v>
+        <v>-0.212685412985899</v>
       </c>
       <c r="I8" t="n">
         <v>-0.792857142857143</v>
@@ -824,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.215067169109523</v>
+        <v>-0.212685412985899</v>
       </c>
       <c r="I9" t="n">
         <v>-0.792857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>0.597014925373134</v>
+        <v>0.592039800995025</v>
       </c>
       <c r="K9" t="n">
-        <v>0.189054726368159</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.445403551661073</v>
+        <v>-3.11721254366308</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3298596061042</v>
+        <v>17.1936916917814</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -898,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -910,16 +904,16 @@
         <v>-0.996415759077198</v>
       </c>
       <c r="J11" t="n">
-        <v>0.194029850746269</v>
+        <v>0.223880597014925</v>
       </c>
       <c r="K11" t="n">
-        <v>0.676616915422886</v>
+        <v>0.63681592039801</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.642910272458131</v>
+        <v>-1.11846062831605</v>
       </c>
       <c r="M11" t="n">
-        <v>2.68465450748882</v>
+        <v>6.8807583321666</v>
       </c>
     </row>
     <row r="12">
@@ -939,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -972,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -984,16 +978,16 @@
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.45771144278607</v>
+        <v>0.358208955223881</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.280512475456089</v>
+        <v>-2.42665957683369</v>
       </c>
       <c r="M13" t="n">
-        <v>0.371759895979774</v>
+        <v>11.4081068747567</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.156979972847309</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="3">
@@ -1048,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.503821522042253</v>
+        <v>0.0642885059677505</v>
       </c>
     </row>
     <row r="5">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.69071475446974</v>
+        <v>-25.8489245466075</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.527771497924401</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="7">
@@ -1092,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.14795918367347</v>
+        <v>-23.4595911189591</v>
       </c>
     </row>
     <row r="9">
@@ -1103,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.311802184071958</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="10">
@@ -1136,7 +1130,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.266913518432413</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="13">
@@ -1147,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.196749171811713</v>
+        <v>-0.264640680495902</v>
       </c>
     </row>
     <row r="14">
@@ -1158,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.297625686610571</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="15">
@@ -1180,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.19245869179633</v>
+        <v>-0.153479900961672</v>
       </c>
     </row>
     <row r="17">
@@ -1191,7 +1185,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.168655942655799</v>
       </c>
     </row>
     <row r="18">
@@ -1202,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.89514507238833</v>
+        <v>-2.56603957638422</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.392825496602283</v>
+        <v>-0.409781098014364</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.272633993500273</v>
+        <v>-0.152871884252284</v>
       </c>
     </row>
     <row r="21">
@@ -1235,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.21848587064969</v>
       </c>
     </row>
     <row r="22">
@@ -1246,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223768279892396</v>
       </c>
     </row>
     <row r="23">
@@ -1257,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.285998411877658</v>
       </c>
     </row>
     <row r="24">
@@ -1301,7 +1295,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.273422341250702</v>
+        <v>-0.955083215680453</v>
       </c>
     </row>
     <row r="28">
@@ -1323,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.186489461104449</v>
+        <v>-0.209442389028095</v>
       </c>
     </row>
     <row r="30">
@@ -1356,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.19382389523262</v>
+        <v>-0.290933989859886</v>
       </c>
     </row>
     <row r="33">
@@ -1367,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.16145621661857</v>
+        <v>-1.03192996774844</v>
       </c>
     </row>
     <row r="34">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.284855879141905</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="35">
@@ -1389,7 +1383,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.68451235645596</v>
+        <v>-2.49746259363127</v>
       </c>
     </row>
     <row r="36">
@@ -1400,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.34021785215426</v>
+        <v>-0.415037877805683</v>
       </c>
     </row>
     <row r="37">
@@ -1411,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.512629692925296</v>
+        <v>0.28994399693336</v>
       </c>
     </row>
     <row r="38">
@@ -1422,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.185899938149074</v>
+        <v>-0.343654127642637</v>
       </c>
     </row>
     <row r="39">
@@ -1433,7 +1427,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.25932273727697</v>
       </c>
     </row>
     <row r="40">
@@ -1444,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.157127817237427</v>
       </c>
     </row>
     <row r="41">
@@ -1455,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.434541724068146</v>
+        <v>-0.378657379632338</v>
       </c>
     </row>
     <row r="42">
@@ -1466,7 +1460,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.440242830157246</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="43">
@@ -1477,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.330236780818266</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="44">
@@ -1488,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.876494190376843</v>
       </c>
     </row>
     <row r="45">
@@ -1499,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.486121298156251</v>
       </c>
     </row>
     <row r="46">
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.292504302990193</v>
+        <v>-0.0377006146233976</v>
       </c>
     </row>
     <row r="47">
@@ -1532,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.63620923892627</v>
+        <v>-0.183435342516554</v>
       </c>
     </row>
     <row r="49">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.170916330637256</v>
+        <v>-0.104305673427609</v>
       </c>
     </row>
     <row r="50">
@@ -1565,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.382971758965195</v>
+        <v>-1.07615443500552</v>
       </c>
     </row>
     <row r="52">
@@ -1576,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-1.67889595622498</v>
+        <v>-0.235661360612498</v>
       </c>
     </row>
     <row r="53">
@@ -1587,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>0.32738414141254</v>
+        <v>0.42369225043923</v>
       </c>
     </row>
     <row r="54">
@@ -1598,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>0.268444788056079</v>
+        <v>0.253127514334449</v>
       </c>
     </row>
     <row r="55">
@@ -1609,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.69760404159705</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.696570434337945</v>
+        <v>-0.456105747515415</v>
       </c>
     </row>
     <row r="58">
@@ -1642,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.854836251857387</v>
+        <v>-1.74426102625209</v>
       </c>
     </row>
     <row r="59">
@@ -1653,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.258757977141055</v>
+        <v>-0.212764802333785</v>
       </c>
     </row>
     <row r="60">
@@ -1675,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.159884498596102</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="62">
@@ -1686,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.75486727335788</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="63">
@@ -1697,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.96281548962603</v>
+        <v>-0.368011839087402</v>
       </c>
     </row>
     <row r="64">
@@ -1708,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.243213483844165</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="65">
@@ -1719,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.151554316068233</v>
+        <v>-0.172541377831095</v>
       </c>
     </row>
     <row r="66">
@@ -1730,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.30651248449465</v>
+        <v>-5.65331027326653</v>
       </c>
     </row>
     <row r="67">
@@ -1741,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.413766116734679</v>
+        <v>-0.398963842715693</v>
       </c>
     </row>
     <row r="68">
@@ -1763,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.201643069586315</v>
       </c>
     </row>
     <row r="70">
@@ -1785,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.213406231570226</v>
+        <v>-0.237281957611143</v>
       </c>
     </row>
     <row r="72">
@@ -1796,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.422671781698962</v>
+        <v>-0.864565285479286</v>
       </c>
     </row>
     <row r="73">
@@ -1807,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.743151803196547</v>
+        <v>-47.0294938543336</v>
       </c>
     </row>
     <row r="74">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.21323478888728</v>
+        <v>-0.189086077585893</v>
       </c>
     </row>
     <row r="75">
@@ -1829,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.181636898909712</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="76">
@@ -1840,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.290509603052532</v>
+        <v>-0.538408730106063</v>
       </c>
     </row>
     <row r="77">
@@ -1862,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.40372095515396</v>
+        <v>-52.0053239979437</v>
       </c>
     </row>
     <row r="79">
@@ -1884,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.192564433020548</v>
+        <v>-0.727002084025332</v>
       </c>
     </row>
     <row r="81">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.326468789151963</v>
+        <v>-0.295087933890422</v>
       </c>
     </row>
     <row r="82">
@@ -1906,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.241269750511099</v>
+        <v>-0.205311628804621</v>
       </c>
     </row>
     <row r="83">
@@ -1917,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.293731599300101</v>
       </c>
     </row>
     <row r="84">
@@ -1928,7 +1922,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.362144877016686</v>
       </c>
     </row>
     <row r="85">
@@ -1939,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.199496064087555</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="86">
@@ -1950,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.156071529620263</v>
+        <v>-0.198608245436354</v>
       </c>
     </row>
     <row r="87">
@@ -1961,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.452765748098826</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="88">
@@ -1972,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.219377349530294</v>
+        <v>-0.189726445328092</v>
       </c>
     </row>
     <row r="89">
@@ -1983,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.00345477325607</v>
       </c>
     </row>
     <row r="90">
@@ -1994,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.152557896144042</v>
+        <v>-0.148180582265036</v>
       </c>
     </row>
     <row r="91">
@@ -2005,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.401979616123361</v>
+        <v>-0.294522880720749</v>
       </c>
     </row>
     <row r="92">
@@ -2016,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.640747214482611</v>
+        <v>-0.397611526861602</v>
       </c>
     </row>
     <row r="93">
@@ -2038,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>0.262837088579166</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="95">
@@ -2049,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.509718239647059</v>
+        <v>-0.758010492030122</v>
       </c>
     </row>
     <row r="96">
@@ -2060,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.318038649936345</v>
       </c>
     </row>
     <row r="97">
@@ -2071,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-2.58625481961377</v>
+        <v>-0.337195732072323</v>
       </c>
     </row>
     <row r="98">
@@ -2082,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.328365661506641</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="99">
@@ -2093,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.161141694313873</v>
+        <v>-0.521053434614134</v>
       </c>
     </row>
     <row r="100">
@@ -2104,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.677900223694108</v>
+        <v>-104.152978492245</v>
       </c>
     </row>
     <row r="101">
@@ -2115,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.771247269635054</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="102">
@@ -2126,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.44246089775073</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="103">
@@ -2137,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.202788830780367</v>
+        <v>-0.129507265619165</v>
       </c>
     </row>
     <row r="104">
@@ -2148,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.806111807552036</v>
+        <v>-0.223843932054164</v>
       </c>
     </row>
     <row r="105">
@@ -2170,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-8.55322525192233</v>
+        <v>-0.174461442805459</v>
       </c>
     </row>
     <row r="107">
@@ -2181,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.394753109158246</v>
       </c>
     </row>
     <row r="108">
@@ -2192,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.33704441772676</v>
       </c>
     </row>
     <row r="109">
@@ -2225,7 +2219,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.192408886442872</v>
+        <v>-0.204063380321197</v>
       </c>
     </row>
     <row r="112">
@@ -2269,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.172254734106236</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="116">
@@ -2302,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.780968564420108</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="119">
@@ -2313,7 +2307,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-5.78523054499507</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="120">
@@ -2324,7 +2318,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.288634789483035</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="121">
@@ -2357,7 +2351,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.30264671902779</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="124">
@@ -2368,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.192115604817514</v>
+        <v>-41.6217395230974</v>
       </c>
     </row>
     <row r="125">
@@ -2379,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.404418541964716</v>
+        <v>-0.302924042867448</v>
       </c>
     </row>
     <row r="126">
@@ -2390,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.721610368147862</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="127">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.229212058628222</v>
+        <v>-0.262476180048302</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.153012969016521</v>
+        <v>-0.153184468677385</v>
       </c>
     </row>
     <row r="129">
@@ -2423,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.658120972495926</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="130">
@@ -2445,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.174022003434655</v>
+        <v>-0.80725611092003</v>
       </c>
     </row>
     <row r="132">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.193629314892417</v>
+        <v>-0.419140166790738</v>
       </c>
     </row>
     <row r="133">
@@ -2478,7 +2472,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.767473917393077</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.483779821745343</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="138">
@@ -2522,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-14.0518893479981</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="139">
@@ -2533,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.315649671329242</v>
+        <v>-0.353728495654036</v>
       </c>
     </row>
     <row r="140">
@@ -2544,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.182541606170024</v>
+        <v>-0.162655449040166</v>
       </c>
     </row>
     <row r="141">
@@ -2555,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.216062773473505</v>
+        <v>-0.466315911004547</v>
       </c>
     </row>
     <row r="142">
@@ -2566,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.180572460247628</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="143">
@@ -2577,7 +2571,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0877594666966655</v>
+        <v>0.224524760043504</v>
       </c>
     </row>
     <row r="144">
@@ -2599,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.190226280232096</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="146">
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.130247275977594</v>
+        <v>-0.168393326688944</v>
       </c>
     </row>
     <row r="147">
@@ -2621,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-6.68815693276835</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="148">
@@ -2643,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.43171915152538</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="150">
@@ -2654,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.370530208971031</v>
+        <v>-0.449282834351664</v>
       </c>
     </row>
     <row r="151">
@@ -2665,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-2.53506684899644</v>
+        <v>-18.6328065055177</v>
       </c>
     </row>
     <row r="152">
@@ -2676,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.437105539586853</v>
       </c>
     </row>
     <row r="153">
@@ -2698,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.496892360074075</v>
+        <v>-0.211088600704721</v>
       </c>
     </row>
     <row r="155">
@@ -2709,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.364905472109455</v>
+        <v>-0.211532899715227</v>
       </c>
     </row>
     <row r="156">
@@ -2731,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.315252694345072</v>
       </c>
     </row>
     <row r="158">
@@ -2742,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.183348533586821</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="159">
@@ -2753,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.172644219646998</v>
+        <v>-2.5691325166578</v>
       </c>
     </row>
     <row r="160">
@@ -2775,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.245250611224784</v>
+        <v>-0.157078765223174</v>
       </c>
     </row>
     <row r="162">
@@ -2786,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-1.37920630141312</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="163">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.3791383971896</v>
+        <v>-3.60423289520996</v>
       </c>
     </row>
     <row r="164">
@@ -2808,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.174723400989014</v>
+        <v>-0.197854620902332</v>
       </c>
     </row>
     <row r="165">
@@ -2819,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.407289404116576</v>
+        <v>-0.177764491405683</v>
       </c>
     </row>
     <row r="166">
@@ -2830,7 +2824,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.436597831655352</v>
       </c>
     </row>
     <row r="167">
@@ -2841,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.220145138303765</v>
+        <v>-0.21028343630835</v>
       </c>
     </row>
     <row r="168">
@@ -2874,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.135062129829179</v>
+        <v>-0.22051860211428</v>
       </c>
     </row>
     <row r="171">
@@ -2896,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.168084774590787</v>
+        <v>-0.168486725076685</v>
       </c>
     </row>
     <row r="173">
@@ -2929,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.605032131254742</v>
+        <v>-0.530769470008838</v>
       </c>
     </row>
     <row r="176">
@@ -2940,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.68255483307658</v>
+        <v>-0.208303078098842</v>
       </c>
     </row>
     <row r="177">
@@ -2951,7 +2945,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.224188888872709</v>
+        <v>-0.209325399910835</v>
       </c>
     </row>
     <row r="178">
@@ -2984,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.168622401735908</v>
+        <v>-0.392283663553333</v>
       </c>
     </row>
     <row r="181">
@@ -2995,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>0.455127846870864</v>
+        <v>0.0237635561053202</v>
       </c>
     </row>
     <row r="182">
@@ -3006,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.408050697686988</v>
+        <v>-0.210129102803265</v>
       </c>
     </row>
     <row r="183">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.0785975092757545</v>
+        <v>-1.18299078365821</v>
       </c>
     </row>
     <row r="184">
@@ -3039,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.216455104510883</v>
+        <v>-0.213584660485848</v>
       </c>
     </row>
     <row r="186">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.497829846818086</v>
+        <v>-0.441747596539767</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.272155755441748</v>
+        <v>-0.33881007701666</v>
       </c>
     </row>
     <row r="188">
@@ -3072,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.396945926128899</v>
+        <v>-0.431719844225315</v>
       </c>
     </row>
     <row r="189">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.191273309262387</v>
+        <v>-0.180034033757839</v>
       </c>
     </row>
     <row r="190">
@@ -3094,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.567408095902852</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="191">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-3.75904323490626</v>
+        <v>-0.769285223858893</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.34801735554619</v>
+        <v>-0.348652347155152</v>
       </c>
     </row>
     <row r="193">
@@ -3160,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>0.105322530816667</v>
+        <v>-3.04492718157339</v>
       </c>
     </row>
     <row r="197">
@@ -3171,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.167565713520398</v>
+        <v>0.072575234053249</v>
       </c>
     </row>
     <row r="198">
@@ -3193,7 +3187,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.658537892223495</v>
       </c>
     </row>
     <row r="200">
@@ -3204,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.189329880109948</v>
+        <v>-0.197580088243318</v>
       </c>
     </row>
     <row r="201">
@@ -3215,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>0.140437790820554</v>
+        <v>-0.265967873114453</v>
       </c>
     </row>
     <row r="202">
@@ -3226,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.688044287229538</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="203">
@@ -3237,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-5.33717931699448</v>
+        <v>-48.9413741006022</v>
       </c>
     </row>
     <row r="204">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.583733132261504</v>
+        <v>-0.511698382287967</v>
       </c>
     </row>
     <row r="205">
@@ -3259,7 +3253,7 @@
         <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.14795918367347</v>
+        <v>-60.3424185285385</v>
       </c>
     </row>
     <row r="206">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.433169507928933</v>
+        <v>-0.94446219921898</v>
       </c>
     </row>
     <row r="207">
@@ -3292,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-1.61136195483634</v>
+        <v>-0.42587540074257</v>
       </c>
     </row>
     <row r="209">
@@ -3303,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-3.4070864142892</v>
+        <v>-0.166007890722752</v>
       </c>
     </row>
     <row r="210">
@@ -3314,7 +3308,7 @@
         <v>16</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.169636214521602</v>
       </c>
     </row>
     <row r="211">
@@ -3336,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.329620861639118</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="213">
@@ -3347,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.170105156528131</v>
+        <v>-0.199607121036212</v>
       </c>
     </row>
     <row r="214">
@@ -3358,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.546901022086723</v>
+        <v>-0.357779658778762</v>
       </c>
     </row>
     <row r="215">
@@ -3402,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>0.0666333059749975</v>
+        <v>-0.180227928919112</v>
       </c>
     </row>
     <row r="219">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.453785622737497</v>
+        <v>-0.161034642634928</v>
       </c>
     </row>
     <row r="220">
@@ -3424,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.244888851644172</v>
+        <v>-0.262895973426541</v>
       </c>
     </row>
     <row r="221">
@@ -3435,7 +3429,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.312077018874844</v>
       </c>
     </row>
     <row r="222">
@@ -3446,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.414874272532651</v>
+        <v>-0.198556888118252</v>
       </c>
     </row>
     <row r="223">
@@ -3457,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.513080894932558</v>
+        <v>-0.640708725445789</v>
       </c>
     </row>
     <row r="224">
@@ -3468,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.194567367318344</v>
+        <v>-0.18833041338</v>
       </c>
     </row>
     <row r="225">
@@ -3501,7 +3495,7 @@
         <v>16</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.362280838281822</v>
+        <v>-0.454369032582693</v>
       </c>
     </row>
     <row r="228">
@@ -3545,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.176497486796489</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="232">
@@ -3556,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.319218441237176</v>
+        <v>-0.413851776620353</v>
       </c>
     </row>
     <row r="233">
@@ -3578,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.170095170880642</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="235">
@@ -3589,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.599065956606916</v>
+        <v>-0.950941138346307</v>
       </c>
     </row>
     <row r="236">
@@ -3600,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.501100339065251</v>
+        <v>-0.397249949773163</v>
       </c>
     </row>
     <row r="237">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.0831904415817639</v>
+        <v>0.196338950195339</v>
       </c>
     </row>
     <row r="238">
@@ -3622,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.398930851034767</v>
+        <v>-0.246820428736652</v>
       </c>
     </row>
     <row r="239">
@@ -3655,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.1471164251303</v>
       </c>
     </row>
     <row r="242">
@@ -3677,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.34179469548183</v>
+        <v>-0.235351841667155</v>
       </c>
     </row>
     <row r="244">
@@ -3688,7 +3682,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.177220705757075</v>
+        <v>-0.063073875892458</v>
       </c>
     </row>
     <row r="245">
@@ -3710,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.18378170547628</v>
       </c>
     </row>
     <row r="247">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.195285121520729</v>
+        <v>-0.202486717497698</v>
       </c>
     </row>
     <row r="250">
@@ -3754,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.236744524403116</v>
+        <v>-0.167418853843871</v>
       </c>
     </row>
     <row r="251">
@@ -3765,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.655045006007458</v>
+        <v>-0.396378759917467</v>
       </c>
     </row>
     <row r="252">
@@ -3776,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>0.0306588839274556</v>
+        <v>-0.19430847454076</v>
       </c>
     </row>
     <row r="253">
@@ -3787,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>0.279775851162848</v>
+        <v>0.0116968135069414</v>
       </c>
     </row>
     <row r="254">
@@ -3798,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.194319556129379</v>
+        <v>-0.172391221389472</v>
       </c>
     </row>
     <row r="255">
@@ -3820,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.513122426396493</v>
+        <v>-0.328382815548006</v>
       </c>
     </row>
     <row r="257">
@@ -3831,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.360362872797596</v>
       </c>
     </row>
     <row r="258">
@@ -3875,7 +3869,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.195337118551818</v>
+        <v>-0.140547635305792</v>
       </c>
     </row>
     <row r="262">
@@ -3886,7 +3880,7 @@
         <v>16</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.67761436958024</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="263">
@@ -3897,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-2.4130196855942</v>
+        <v>-8.83898527830489</v>
       </c>
     </row>
     <row r="264">
@@ -3919,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.178431076273465</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="266">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.05590878123802</v>
+        <v>-5.39369684416665</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.346991229090747</v>
+        <v>-4.36421094108183</v>
       </c>
     </row>
     <row r="268">
@@ -3952,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.193712722849879</v>
+        <v>-0.458721661498245</v>
       </c>
     </row>
     <row r="269">
@@ -3974,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.153707550464457</v>
+        <v>-0.165044058398921</v>
       </c>
     </row>
     <row r="271">
@@ -3996,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.246618557095834</v>
+        <v>-1.10710238334462</v>
       </c>
     </row>
     <row r="273">
@@ -4007,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.14795918367347</v>
+        <v>-63.6087491872174</v>
       </c>
     </row>
     <row r="274">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-1.71426013313959</v>
+        <v>-0.159600998207141</v>
       </c>
     </row>
     <row r="275">
@@ -4029,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-5.45195408807121</v>
+        <v>-0.233478313504351</v>
       </c>
     </row>
     <row r="276">
@@ -4040,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.54128646467936</v>
+        <v>-0.778607784932455</v>
       </c>
     </row>
     <row r="277">
@@ -4051,7 +4045,7 @@
         <v>16</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.226888165232212</v>
       </c>
     </row>
     <row r="278">
@@ -4084,7 +4078,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.159146023498175</v>
       </c>
     </row>
     <row r="281">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0102327850630679</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="282">
@@ -4117,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.70464913069096</v>
+        <v>-0.313857515435818</v>
       </c>
     </row>
     <row r="284">
@@ -4128,7 +4122,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.167485777539646</v>
+        <v>-0.250248923961215</v>
       </c>
     </row>
     <row r="285">
@@ -4139,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.275070072076512</v>
+        <v>-0.973352396412625</v>
       </c>
     </row>
     <row r="286">
@@ -4150,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.157580041938759</v>
+        <v>-0.33738847529341</v>
       </c>
     </row>
     <row r="287">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.376220667643133</v>
       </c>
     </row>
     <row r="288">
@@ -4172,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.230345614120588</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="289">
@@ -4194,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.293802944097769</v>
+        <v>-0.0392794364019873</v>
       </c>
     </row>
     <row r="291">
@@ -4205,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.205561356037332</v>
+        <v>-0.24243082728508</v>
       </c>
     </row>
     <row r="292">
@@ -4216,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.461310614521818</v>
+        <v>-25.8637382931</v>
       </c>
     </row>
     <row r="293">
@@ -4238,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.177555711907225</v>
+        <v>-0.800666376834418</v>
       </c>
     </row>
     <row r="295">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.247433843756848</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="296">
@@ -4260,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-6.80278407404013</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="297">
@@ -4293,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.217278063224371</v>
+        <v>-0.539298919634662</v>
       </c>
     </row>
     <row r="300">
@@ -4304,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.789896478751874</v>
+        <v>-51.8874633576263</v>
       </c>
     </row>
     <row r="301">
@@ -4326,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-6.4285323399484</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="303">
@@ -4337,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.659341518259426</v>
+        <v>-1.33712036812061</v>
       </c>
     </row>
     <row r="304">
@@ -4348,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.232272226565923</v>
+        <v>-0.29518601109277</v>
       </c>
     </row>
     <row r="305">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.480537435965615</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="310">
@@ -4414,7 +4408,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.191354380359177</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="311">
@@ -4425,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.271908080979154</v>
       </c>
     </row>
     <row r="312">
@@ -4436,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.147959183673469</v>
+        <v>-51.8649255019783</v>
       </c>
     </row>
     <row r="313">
@@ -4447,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-4.62846455115692</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="314">
@@ -4458,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.275444544164741</v>
       </c>
     </row>
     <row r="315">
@@ -4513,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-6.98345692384652</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="320">
@@ -4524,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.682005904999886</v>
       </c>
     </row>
     <row r="321">
@@ -4546,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.191931880006506</v>
+        <v>-0.210896206540944</v>
       </c>
     </row>
     <row r="323">
@@ -4579,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.561109386349381</v>
+        <v>0.340451508391001</v>
       </c>
     </row>
     <row r="326">
@@ -4590,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.291807032500498</v>
+        <v>-0.465316914493038</v>
       </c>
     </row>
     <row r="327">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.271297557118963</v>
+        <v>-0.560686273185675</v>
       </c>
     </row>
     <row r="328">
@@ -4612,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.360311472567789</v>
+        <v>-0.442088907068757</v>
       </c>
     </row>
     <row r="329">
@@ -4645,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>0.103537157165503</v>
+        <v>-0.189754686626792</v>
       </c>
     </row>
     <row r="332">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.54281456068285</v>
+        <v>-0.558569610373762</v>
       </c>
     </row>
     <row r="333">
@@ -4667,7 +4661,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.245525283721767</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="334">
@@ -4678,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.544697690171532</v>
       </c>
     </row>
     <row r="335">
@@ -4689,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.487866854552929</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="336">
@@ -4700,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.582333897768116</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="337">
@@ -4711,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.181593258541769</v>
       </c>
     </row>
     <row r="338">
@@ -4722,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.0274695206376105</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="339">
@@ -4733,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.27526345055223</v>
+        <v>-0.276915514284187</v>
       </c>
     </row>
     <row r="340">
@@ -4744,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.264791011024058</v>
+        <v>-0.235576437898391</v>
       </c>
     </row>
     <row r="341">
@@ -4755,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.156831687960411</v>
       </c>
     </row>
     <row r="342">
@@ -4766,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.249687853556128</v>
       </c>
     </row>
     <row r="343">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-1.36596998086643</v>
+        <v>-0.39287553448561</v>
       </c>
     </row>
     <row r="344">
@@ -4810,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.167458791738257</v>
+        <v>-0.172825916908523</v>
       </c>
     </row>
     <row r="347">
@@ -4821,7 +4815,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.980151699691519</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="348">
@@ -4832,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.187382750202451</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="349">
@@ -4854,7 +4848,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-1.28597717732741</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="351">
@@ -4865,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.358868196908241</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="352">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.288626520993108</v>
+        <v>-0.487789042091388</v>
       </c>
     </row>
     <row r="353">
@@ -4887,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.159758146702356</v>
+        <v>-0.894712451873572</v>
       </c>
     </row>
     <row r="354">
@@ -4898,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.180158769774719</v>
+        <v>-0.197889073296534</v>
       </c>
     </row>
     <row r="355">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.995288186237274</v>
+        <v>-0.848563025623041</v>
       </c>
     </row>
     <row r="357">
@@ -4931,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.450035295655014</v>
+        <v>-0.561846258209111</v>
       </c>
     </row>
     <row r="358">
@@ -4953,7 +4947,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.163787332108739</v>
+        <v>-0.102127672304662</v>
       </c>
     </row>
     <row r="360">
@@ -4964,7 +4958,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.871893649543675</v>
+        <v>-2.15673317732415</v>
       </c>
     </row>
     <row r="361">
@@ -4997,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.160925446617574</v>
+        <v>-0.29232724743114</v>
       </c>
     </row>
     <row r="364">
@@ -5008,7 +5002,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.183876021035488</v>
+        <v>-0.192133500993546</v>
       </c>
     </row>
     <row r="365">
@@ -5019,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.244399454318947</v>
       </c>
     </row>
     <row r="366">
@@ -5030,7 +5024,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.65477727272119</v>
+        <v>-0.323675579046832</v>
       </c>
     </row>
     <row r="367">
@@ -5041,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.00616820037168431</v>
+        <v>-0.247535260481784</v>
       </c>
     </row>
     <row r="368">
@@ -5052,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.332853455177438</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="369">
@@ -5063,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.748401757792639</v>
       </c>
     </row>
     <row r="370">
@@ -5074,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-1.03963938951673</v>
+        <v>-0.462086577568484</v>
       </c>
     </row>
     <row r="371">
@@ -5096,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.244545080034249</v>
+        <v>-0.180457680956094</v>
       </c>
     </row>
     <row r="373">
@@ -5107,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.16563941710293</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="374">
@@ -5129,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.859357196051052</v>
+        <v>-0.0977292109248522</v>
       </c>
     </row>
     <row r="376">
@@ -5140,7 +5134,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.200908985316089</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="377">
@@ -5151,7 +5145,7 @@
         <v>16</v>
       </c>
       <c r="C377" t="n">
-        <v>-0.176579002541639</v>
+        <v>-0.162306326858386</v>
       </c>
     </row>
     <row r="378">
@@ -5173,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.361761757765146</v>
       </c>
     </row>
     <row r="380">
@@ -5184,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.271147396887291</v>
+        <v>-0.270871688734459</v>
       </c>
     </row>
     <row r="381">
@@ -5195,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.329508754553609</v>
+        <v>-0.16026178225428</v>
       </c>
     </row>
     <row r="382">
@@ -5206,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.343084908719121</v>
+        <v>-0.369876537371357</v>
       </c>
     </row>
     <row r="383">
@@ -5217,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.39989816035577</v>
       </c>
     </row>
     <row r="384">
@@ -5239,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.157973036901513</v>
       </c>
     </row>
     <row r="386">
@@ -5250,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-1.00069666321336</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="387">
@@ -5261,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.726882942003501</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="388">
@@ -5272,7 +5266,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.310563877199542</v>
+        <v>-1.26245892337556</v>
       </c>
     </row>
     <row r="389">
@@ -5283,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.157756957611029</v>
+        <v>-0.119753706116321</v>
       </c>
     </row>
     <row r="390">
@@ -5294,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.218997450519519</v>
+        <v>-48.1281600708381</v>
       </c>
     </row>
     <row r="391">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.190069150210214</v>
+        <v>-0.703192237346032</v>
       </c>
     </row>
     <row r="392">
@@ -5316,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.376691690005693</v>
+        <v>-0.23204758909261</v>
       </c>
     </row>
     <row r="393">
@@ -5338,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.70234190527299</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="395">
@@ -5360,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.278446303506222</v>
+        <v>-0.129598146137951</v>
       </c>
     </row>
     <row r="397">
@@ -5371,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.439061758773424</v>
       </c>
     </row>
     <row r="398">
@@ -5382,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-2.22622240788757</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="399">
@@ -5393,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-4.82696050000188</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="400">
@@ -5404,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.202997546691711</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="401">
@@ -5415,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-4.88885492372136</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="402">
@@ -5426,7 +5420,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.229301119617989</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="403">
@@ -5437,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-14.2302577097167</v>
+        <v>-42.5537212220395</v>
       </c>
     </row>
     <row r="404">
@@ -5448,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.612905778317324</v>
+        <v>-0.425441003046483</v>
       </c>
     </row>
     <row r="405">
@@ -5459,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.383284031227479</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="406">
@@ -5470,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.423080506687281</v>
+        <v>-50.7231977823126</v>
       </c>
     </row>
     <row r="407">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>0.93901910221677</v>
+        <v>-3.34707553228183</v>
       </c>
     </row>
     <row r="409">
@@ -5514,7 +5508,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-2.676317509074</v>
+        <v>-0.156009715041646</v>
       </c>
     </row>
     <row r="411">
@@ -5536,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.261199323211077</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="413">
@@ -5558,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.0057405284163</v>
       </c>
     </row>
     <row r="415">
@@ -5591,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.438883978166887</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="418">
@@ -5602,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.157018857122602</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="419">
@@ -5613,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.584785950026733</v>
+        <v>-0.541512612505845</v>
       </c>
     </row>
     <row r="420">
@@ -5624,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>0.332531861751746</v>
+        <v>0.126141296770476</v>
       </c>
     </row>
     <row r="421">
@@ -5635,7 +5629,7 @@
         <v>16</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.316769674830452</v>
       </c>
     </row>
     <row r="422">
@@ -5646,7 +5640,7 @@
         <v>16</v>
       </c>
       <c r="C422" t="n">
-        <v>-0.205882419234578</v>
+        <v>-0.208403697488606</v>
       </c>
     </row>
     <row r="423">
@@ -5657,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-1.78005759887035</v>
+        <v>-0.761842335027515</v>
       </c>
     </row>
     <row r="424">
@@ -5668,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.196297021632718</v>
+        <v>-0.268822648894659</v>
       </c>
     </row>
     <row r="425">
@@ -5679,7 +5673,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-5.9542719311294</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="426">
@@ -5690,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.482612852208073</v>
       </c>
     </row>
     <row r="427">
@@ -5701,7 +5695,7 @@
         <v>16</v>
       </c>
       <c r="C427" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.98649203192669</v>
       </c>
     </row>
     <row r="428">
@@ -5712,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.43718914858966</v>
       </c>
     </row>
     <row r="429">
@@ -5723,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.719270662510921</v>
       </c>
     </row>
     <row r="430">
@@ -5756,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.274913589456912</v>
       </c>
     </row>
     <row r="433">
@@ -5778,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.15659841313457</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="435">
@@ -5789,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.448997965382701</v>
+        <v>-0.947616730718225</v>
       </c>
     </row>
     <row r="436">
@@ -5800,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.428334177060618</v>
+        <v>-0.213148500620686</v>
       </c>
     </row>
     <row r="437">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.0692690608654318</v>
+        <v>0.34195819502202</v>
       </c>
     </row>
     <row r="438">
@@ -5822,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.627307150380465</v>
+        <v>-0.308249505648581</v>
       </c>
     </row>
     <row r="439">
@@ -5833,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.399190344837973</v>
+        <v>-0.507629273633734</v>
       </c>
     </row>
     <row r="440">
@@ -5844,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.445366571680531</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="441">
@@ -5855,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.819341145449517</v>
       </c>
     </row>
     <row r="442">
@@ -5877,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.538321804248332</v>
+        <v>-0.197078983816428</v>
       </c>
     </row>
     <row r="444">
@@ -5888,7 +5882,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.183416124998388</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="445">
@@ -5899,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.589965050777846</v>
       </c>
     </row>
     <row r="446">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.240469885162224</v>
       </c>
     </row>
     <row r="450">
@@ -5954,7 +5948,7 @@
         <v>16</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.189615100386407</v>
+        <v>-0.158860966513894</v>
       </c>
     </row>
     <row r="451">
@@ -5965,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.518719802069591</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="452">
@@ -5976,7 +5970,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.92351797035758</v>
+        <v>-0.169014460615797</v>
       </c>
     </row>
     <row r="453">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>0.170320106866964</v>
+        <v>0.119655021554126</v>
       </c>
     </row>
     <row r="454">
@@ -6020,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.338232357135702</v>
+        <v>-0.894029573042088</v>
       </c>
     </row>
     <row r="457">
@@ -6031,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.531740874080905</v>
       </c>
     </row>
     <row r="458">
@@ -6042,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.374686299730866</v>
       </c>
     </row>
     <row r="459">
@@ -6075,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.147371674645413</v>
       </c>
     </row>
     <row r="462">
@@ -6119,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.222460922212864</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="466">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-3.78849950978285</v>
+        <v>-0.241834454235572</v>
       </c>
     </row>
     <row r="467">
@@ -6141,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.19399767363595</v>
+        <v>-27.2410703808022</v>
       </c>
     </row>
     <row r="468">
@@ -6174,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.19206544652422</v>
+        <v>-0.204423117829131</v>
       </c>
     </row>
     <row r="471">
@@ -6196,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.193543578451746</v>
+        <v>-1.33559329295353</v>
       </c>
     </row>
     <row r="473">
@@ -6207,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.58754910798189</v>
+        <v>-44.0573446942894</v>
       </c>
     </row>
     <row r="474">
@@ -6218,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.23827057775517</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="475">
@@ -6229,7 +6223,7 @@
         <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.342701571852442</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="476">
@@ -6240,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.543563610043921</v>
       </c>
     </row>
     <row r="477">
@@ -6251,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.316162834264289</v>
+        <v>-0.529817408699454</v>
       </c>
     </row>
     <row r="478">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.105577782104466</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="482">
@@ -6306,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.155574669663086</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="483">
@@ -6317,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.589340019458646</v>
       </c>
     </row>
     <row r="484">
@@ -6328,7 +6322,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.330132889794087</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="485">
@@ -6339,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.17904159609131</v>
+        <v>-17.1158455357519</v>
       </c>
     </row>
     <row r="486">
@@ -6350,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.256985272908189</v>
+        <v>-0.402403658353522</v>
       </c>
     </row>
     <row r="487">
@@ -6372,7 +6366,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.273791098928669</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="489">
@@ -6394,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.256182200346557</v>
+        <v>-0.138787330076087</v>
       </c>
     </row>
     <row r="491">
@@ -6405,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-1.42138263481264</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="492">
@@ -6416,7 +6410,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.500262308057602</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="493">
@@ -6438,7 +6432,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.198644645772644</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="495">
@@ -6449,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.287842408026879</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="496">
@@ -6460,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>-4.42647368779817</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="497">
@@ -6471,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.374127676929416</v>
       </c>
     </row>
     <row r="498">
@@ -6493,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.254675528652409</v>
+        <v>-0.690022950394829</v>
       </c>
     </row>
     <row r="500">
@@ -6504,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.715125897616231</v>
+        <v>-26.1231864241834</v>
       </c>
     </row>
     <row r="501">
@@ -6526,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-3.90606504852639</v>
+        <v>-0.344680436575436</v>
       </c>
     </row>
     <row r="503">
@@ -6537,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.220963370354279</v>
+        <v>-0.437203715890719</v>
       </c>
     </row>
     <row r="504">
@@ -6548,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.151423850927805</v>
       </c>
     </row>
     <row r="505">
@@ -6570,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-3.54477523551381</v>
+        <v>-0.24773219603023</v>
       </c>
     </row>
     <row r="507">
@@ -6581,7 +6575,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.387662612923039</v>
       </c>
     </row>
     <row r="508">
@@ -6592,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.699622567168409</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="509">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.326866422393668</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="510">
@@ -6625,7 +6619,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.211247649577532</v>
+        <v>-0.198301252862451</v>
       </c>
     </row>
     <row r="512">
@@ -6647,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.589817376613265</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="514">
@@ -6669,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.287585639408636</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="516">
@@ -6691,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.289389418350216</v>
       </c>
     </row>
     <row r="518">
@@ -6746,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.247872996699299</v>
+        <v>-0.213517403965961</v>
       </c>
     </row>
     <row r="523">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.325154228477749</v>
+        <v>-0.230431405193593</v>
       </c>
     </row>
     <row r="525">
@@ -6779,7 +6773,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.192041083843101</v>
+        <v>-0.21127180498688</v>
       </c>
     </row>
     <row r="526">
@@ -6790,7 +6784,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.339890988668047</v>
+        <v>-0.324926784398798</v>
       </c>
     </row>
     <row r="527">
@@ -6801,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.174577937496452</v>
+        <v>-0.181207416825275</v>
       </c>
     </row>
     <row r="528">
@@ -6812,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.289063910876751</v>
+        <v>-0.252990138812298</v>
       </c>
     </row>
     <row r="529">
@@ -6845,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.187255250625559</v>
+        <v>-0.414317127595107</v>
       </c>
     </row>
     <row r="532">
@@ -6856,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-1.611836691666</v>
+        <v>-2.43702142983685</v>
       </c>
     </row>
     <row r="533">
@@ -6878,7 +6872,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-29.2052042568077</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="535">
@@ -6889,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.517743223888607</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="536">
@@ -6900,7 +6894,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>0.18518086362034</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="537">
@@ -6911,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.188101162754083</v>
       </c>
     </row>
     <row r="538">
@@ -6922,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>0.337015439937373</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="539">
@@ -6933,7 +6927,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.21954724848297</v>
+        <v>-0.243453552276109</v>
       </c>
     </row>
     <row r="540">
@@ -6944,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.65665223812461</v>
       </c>
     </row>
     <row r="541">
@@ -6955,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.86461504876381</v>
       </c>
     </row>
     <row r="542">
@@ -6966,7 +6960,7 @@
         <v>16</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.30848346915279</v>
+        <v>-0.23453268895006</v>
       </c>
     </row>
     <row r="543">
@@ -6977,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.16535016435721</v>
+        <v>-0.36042604779623</v>
       </c>
     </row>
     <row r="544">
@@ -7010,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.989739161614734</v>
+        <v>-0.396557195961596</v>
       </c>
     </row>
     <row r="547">
@@ -7021,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.34617658637365</v>
+        <v>-0.80420483578187</v>
       </c>
     </row>
     <row r="548">
@@ -7032,7 +7026,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.195226972211414</v>
       </c>
     </row>
     <row r="549">
@@ -7043,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.40940761518132</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="550">
@@ -7054,7 +7048,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-1.029834561103</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="551">
@@ -7065,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.266390993972696</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="552">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.218625575080786</v>
+        <v>-0.212972792241519</v>
       </c>
     </row>
     <row r="553">
@@ -7087,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.35466150594725</v>
+        <v>-0.55062510062622</v>
       </c>
     </row>
     <row r="554">
@@ -7098,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-2.73152674689012</v>
+        <v>-0.295915226741053</v>
       </c>
     </row>
     <row r="555">
@@ -7109,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.777766623345095</v>
       </c>
     </row>
     <row r="556">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-4.59527120545741</v>
+        <v>-0.738010057528139</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.558387911646722</v>
+        <v>-0.319483872220442</v>
       </c>
     </row>
     <row r="558">
@@ -7142,7 +7136,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.24805652479061</v>
       </c>
     </row>
     <row r="559">
@@ -7153,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.135869317879911</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="560">
@@ -7164,7 +7158,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-1.55014919536306</v>
+        <v>-0.542436173740885</v>
       </c>
     </row>
     <row r="561">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.317728748568184</v>
       </c>
     </row>
     <row r="564">
@@ -7208,7 +7202,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.456883889859785</v>
+        <v>-0.171286428300103</v>
       </c>
     </row>
     <row r="565">
@@ -7219,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.253910374605054</v>
       </c>
     </row>
     <row r="566">
@@ -7241,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.156243464517081</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7263,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.572305958051394</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="570">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.566386906294034</v>
+        <v>-0.516571763758755</v>
       </c>
     </row>
     <row r="571">
@@ -7296,7 +7290,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.953069688055249</v>
+        <v>-0.306067171267175</v>
       </c>
     </row>
     <row r="573">
@@ -7307,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.44426325856649</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="574">
@@ -7329,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.18878787000149</v>
+        <v>-0.476317132769469</v>
       </c>
     </row>
     <row r="576">
@@ -7340,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.226855625308336</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="577">
@@ -7373,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.317737593833137</v>
       </c>
     </row>
     <row r="580">
@@ -7384,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.442389419117155</v>
+        <v>-0.254754737851981</v>
       </c>
     </row>
     <row r="581">
@@ -7395,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.214256852567477</v>
+        <v>-0.137780202251456</v>
       </c>
     </row>
     <row r="582">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>0.240441066845991</v>
+        <v>-0.335228888388886</v>
       </c>
     </row>
     <row r="583">
@@ -7417,7 +7411,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.17848249862425</v>
+        <v>-0.222120022458552</v>
       </c>
     </row>
     <row r="584">
@@ -7450,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.404694429935747</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="587">
@@ -7461,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.687007074447349</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="588">
@@ -7472,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.245054919727767</v>
+        <v>-0.210742917721214</v>
       </c>
     </row>
     <row r="589">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.120334523230813</v>
+        <v>-0.167966548486998</v>
       </c>
     </row>
     <row r="590">
@@ -7494,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.168759363673661</v>
+        <v>-0.274215157937878</v>
       </c>
     </row>
     <row r="591">
@@ -7505,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.229997699873459</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="592">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.271538887100244</v>
+        <v>-0.230955853989703</v>
       </c>
     </row>
     <row r="593">
@@ -7538,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.728873563190827</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="595">
@@ -7560,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.266393985100608</v>
+        <v>-0.771266966284972</v>
       </c>
     </row>
     <row r="597">
@@ -7571,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.476179790991386</v>
+        <v>-0.239280597171322</v>
       </c>
     </row>
     <row r="598">
@@ -7582,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.303946964932813</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="599">
@@ -7593,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-1.89457320157894</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="600">
@@ -7615,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.240628074798971</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="602">
@@ -7626,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>-0.147959183673469</v>
+        <v>-96.3776736253416</v>
       </c>
     </row>
     <row r="603">
@@ -7659,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.217546877505528</v>
+        <v>-99.0233160627913</v>
       </c>
     </row>
     <row r="606">
@@ -7670,7 +7664,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.64320408379596</v>
+        <v>-0.223532341142046</v>
       </c>
     </row>
     <row r="607">
@@ -7681,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.510483754256542</v>
+        <v>-1.17483947752107</v>
       </c>
     </row>
     <row r="608">
@@ -7703,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.154408090020807</v>
+        <v>-0.858237302292916</v>
       </c>
     </row>
     <row r="610">
@@ -7714,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.26810184176105</v>
+        <v>-0.243497476009915</v>
       </c>
     </row>
     <row r="611">
@@ -7725,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-1.7478843366143</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="612">
@@ -7747,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>0.475123341835607</v>
+        <v>-0.158263586113262</v>
       </c>
     </row>
     <row r="614">
@@ -7780,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>0.479493127991279</v>
+        <v>-0.157377680555193</v>
       </c>
     </row>
     <row r="617">
@@ -7802,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>0.0299043925206602</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="619">
@@ -7813,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-1.76265640226403</v>
+        <v>-1.75285073544079</v>
       </c>
     </row>
     <row r="620">
@@ -7824,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.123012018763935</v>
+        <v>-0.132879603357806</v>
       </c>
     </row>
     <row r="621">
@@ -7835,7 +7829,7 @@
         <v>16</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.243024353298487</v>
+        <v>-0.13334398721162</v>
       </c>
     </row>
     <row r="622">
@@ -7846,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.762683239799464</v>
       </c>
     </row>
     <row r="623">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.427598335454444</v>
+        <v>-0.397387857374562</v>
       </c>
     </row>
     <row r="625">
@@ -7879,7 +7873,7 @@
         <v>16</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.403684687373194</v>
+        <v>-0.153617225922446</v>
       </c>
     </row>
     <row r="626">
@@ -7890,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.6521587006558</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="627">
@@ -7901,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.20552941096906</v>
       </c>
     </row>
     <row r="628">
@@ -7912,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.280476712535071</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="629">
@@ -7923,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.684063579186069</v>
+        <v>-0.162807244588124</v>
       </c>
     </row>
     <row r="630">
@@ -7934,7 +7928,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.34188251516811</v>
+        <v>-0.705463338828766</v>
       </c>
     </row>
     <row r="631">
@@ -7945,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.201152469761129</v>
       </c>
     </row>
     <row r="632">
@@ -7956,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-2.39766047855096</v>
+        <v>-0.408279424444655</v>
       </c>
     </row>
     <row r="633">
@@ -7967,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.43965251303329</v>
+        <v>-2.36765213330388</v>
       </c>
     </row>
     <row r="634">
@@ -7978,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.210149309209245</v>
       </c>
     </row>
     <row r="635">
@@ -7989,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.266167286046278</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="636">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.283521772351001</v>
       </c>
     </row>
     <row r="637">
@@ -8011,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.160094986802333</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="638">
@@ -8033,7 +8027,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.241283425741881</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="640">
@@ -8044,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.62431205732338</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="641">
@@ -8055,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.326287940108182</v>
+        <v>-0.310666433536968</v>
       </c>
     </row>
     <row r="642">
@@ -8066,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.508430846193565</v>
+        <v>-21.5447130900624</v>
       </c>
     </row>
     <row r="643">
@@ -8077,7 +8071,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.33802067613032</v>
+        <v>-0.172328533588684</v>
       </c>
     </row>
     <row r="644">
@@ -8088,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.448057577488683</v>
       </c>
     </row>
     <row r="645">
@@ -8099,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.389385232748281</v>
+        <v>-0.437010253518509</v>
       </c>
     </row>
     <row r="646">
@@ -8110,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.0792795621618068</v>
+        <v>-0.118504006565069</v>
       </c>
     </row>
     <row r="647">
@@ -8121,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.3983923941162</v>
+        <v>-0.10090376886108</v>
       </c>
     </row>
     <row r="648">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.200306036478038</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="649">
@@ -8143,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-1.02215956296586</v>
+        <v>-0.171391790928178</v>
       </c>
     </row>
     <row r="650">
@@ -8154,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-1.31084745114428</v>
+        <v>-0.218545814483965</v>
       </c>
     </row>
     <row r="651">
@@ -8165,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.306888968810546</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="652">
@@ -8176,7 +8170,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.209699269398338</v>
+        <v>-2.34631345770289</v>
       </c>
     </row>
     <row r="653">
@@ -8187,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.203246477569012</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8209,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.182183821144182</v>
+        <v>-0.3370865878378</v>
       </c>
     </row>
     <row r="656">
@@ -8231,7 +8225,7 @@
         <v>16</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.356381962879353</v>
       </c>
     </row>
     <row r="658">
@@ -8253,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.184801109416169</v>
+        <v>-0.229335443473511</v>
       </c>
     </row>
     <row r="660">
@@ -8264,7 +8258,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.452188807696994</v>
       </c>
     </row>
     <row r="661">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.558008631668021</v>
+        <v>-0.31540710225899</v>
       </c>
     </row>
     <row r="662">
@@ -8286,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.20261108255616</v>
+        <v>-0.225936657978161</v>
       </c>
     </row>
     <row r="663">
@@ -8297,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.294664939273757</v>
       </c>
     </row>
     <row r="664">
@@ -8308,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.49774616482994</v>
+        <v>-5.61682797662847</v>
       </c>
     </row>
     <row r="665">
@@ -8319,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.849583852517964</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="666">
@@ -8330,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.38830455586174</v>
       </c>
     </row>
     <row r="667">
@@ -8341,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.36507536334155</v>
       </c>
     </row>
     <row r="668">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-1.30367079341441</v>
+        <v>-1.81589663044716</v>
       </c>
     </row>
     <row r="673">
@@ -8407,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.147502324376679</v>
+        <v>-0.278083481539975</v>
       </c>
     </row>
     <row r="674">
@@ -8418,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.27322638611965</v>
       </c>
     </row>
     <row r="675">
@@ -8451,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.366151725255567</v>
+        <v>-0.0973028172761152</v>
       </c>
     </row>
     <row r="678">
@@ -8462,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.122522785318415</v>
+        <v>-0.145491419831988</v>
       </c>
     </row>
     <row r="679">
@@ -8473,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.622674766658858</v>
+        <v>-0.389694288107572</v>
       </c>
     </row>
     <row r="680">
@@ -8484,7 +8478,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.403925309905051</v>
+        <v>-0.223754257671104</v>
       </c>
     </row>
     <row r="681">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>0.0557683383311851</v>
+        <v>-0.300122795880093</v>
       </c>
     </row>
     <row r="682">
@@ -8506,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-17.5606974480272</v>
+        <v>-0.699060495942918</v>
       </c>
     </row>
     <row r="683">
@@ -8517,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.300802712040578</v>
       </c>
     </row>
     <row r="684">
@@ -8528,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.52470012362275</v>
+        <v>-0.261252798335572</v>
       </c>
     </row>
     <row r="685">
@@ -8539,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.524015163342977</v>
+        <v>-0.151497127629344</v>
       </c>
     </row>
     <row r="686">
@@ -8572,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.483970813995624</v>
+        <v>-0.16802923106764</v>
       </c>
     </row>
     <row r="689">
@@ -8616,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.8746196462089</v>
+        <v>-184.504933579539</v>
       </c>
     </row>
     <row r="693">
@@ -8627,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.141134769170266</v>
+        <v>-0.217747220108677</v>
       </c>
     </row>
     <row r="694">
@@ -8649,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.871519389884771</v>
+        <v>-0.266714952714532</v>
       </c>
     </row>
     <row r="696">
@@ -8660,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.417539194311093</v>
+        <v>-0.173773438258064</v>
       </c>
     </row>
     <row r="697">
@@ -8682,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.499870263519949</v>
       </c>
     </row>
     <row r="699">
@@ -8693,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-2.19706579747916</v>
+        <v>0.0743463533864793</v>
       </c>
     </row>
     <row r="700">
@@ -8704,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.685637074951061</v>
+        <v>-0.312104039935623</v>
       </c>
     </row>
     <row r="701">
@@ -8726,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.147959183673469</v>
+        <v>0.640181169015975</v>
       </c>
     </row>
     <row r="703">
@@ -8737,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.109722910098531</v>
       </c>
     </row>
     <row r="704">
@@ -8759,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.200448401238518</v>
+        <v>-0.476500435087483</v>
       </c>
     </row>
     <row r="706">
@@ -8770,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-3.12535986165557</v>
+        <v>-0.510698000696084</v>
       </c>
     </row>
     <row r="707">
@@ -8781,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.366685218628368</v>
+        <v>-0.129940708946703</v>
       </c>
     </row>
     <row r="708">
@@ -8792,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.187912225076648</v>
+        <v>-0.190008736605551</v>
       </c>
     </row>
     <row r="709">
@@ -8803,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.176853746392384</v>
       </c>
     </row>
     <row r="710">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.348459141468275</v>
+        <v>-0.232513314607498</v>
       </c>
     </row>
     <row r="711">
@@ -8825,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-4.56089586005806</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="712">
@@ -8858,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.409460331854091</v>
+        <v>-0.173199908630531</v>
       </c>
     </row>
     <row r="715">
@@ -8869,7 +8863,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.186521790945028</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="716">
@@ -8880,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.875172544492518</v>
+        <v>-0.215008676181789</v>
       </c>
     </row>
     <row r="717">
@@ -8891,7 +8885,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.266140182910271</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="718">
@@ -8902,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.144885443446522</v>
+        <v>-0.311765376997181</v>
       </c>
     </row>
     <row r="719">
@@ -8913,7 +8907,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.22408311554626</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="720">
@@ -8935,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-2.19410334131845</v>
+        <v>-3.11897119449901</v>
       </c>
     </row>
     <row r="722">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.354507214145563</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="723">
@@ -8957,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.446381153849619</v>
+        <v>-0.231691646559827</v>
       </c>
     </row>
     <row r="724">
@@ -8968,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.334920677998649</v>
       </c>
     </row>
     <row r="725">
@@ -8979,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.496107794972902</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="726">
@@ -8990,7 +8984,7 @@
         <v>16</v>
       </c>
       <c r="C726" t="n">
-        <v>0.0894610342688982</v>
+        <v>0.785325319922514</v>
       </c>
     </row>
     <row r="727">
@@ -9001,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.75697802958369</v>
       </c>
     </row>
     <row r="728">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.219178908812131</v>
       </c>
     </row>
     <row r="730">
@@ -9067,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.190287049918616</v>
       </c>
     </row>
     <row r="734">
@@ -9111,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.804159807611645</v>
+        <v>-0.594875683060268</v>
       </c>
     </row>
     <row r="738">
@@ -9122,7 +9116,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.426868950190394</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="739">
@@ -9133,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>0.103090794932357</v>
+        <v>-73.3418297992261</v>
       </c>
     </row>
     <row r="740">
@@ -9144,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.358668644868112</v>
+        <v>-0.372825552272677</v>
       </c>
     </row>
     <row r="741">
@@ -9155,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.246635069444459</v>
+        <v>-0.162578931619341</v>
       </c>
     </row>
     <row r="742">
@@ -9166,7 +9160,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.490003678619245</v>
+        <v>-0.150419464238625</v>
       </c>
     </row>
     <row r="743">
@@ -9177,7 +9171,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.362373692903332</v>
+        <v>-0.654869907155195</v>
       </c>
     </row>
     <row r="744">
@@ -9188,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.191501716240159</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="745">
@@ -9243,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.180551969915147</v>
+        <v>-0.242545735619957</v>
       </c>
     </row>
     <row r="750">
@@ -9265,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.174865523054706</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="752">
@@ -9298,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.184952432262395</v>
       </c>
     </row>
     <row r="755">
@@ -9309,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.185580343672603</v>
+        <v>-0.16425519234549</v>
       </c>
     </row>
     <row r="756">
@@ -9342,7 +9336,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.189218718853025</v>
+        <v>-0.221255777089155</v>
       </c>
     </row>
     <row r="759">
@@ -9353,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.235224366192779</v>
+        <v>-6.0322630268318</v>
       </c>
     </row>
     <row r="760">
@@ -9364,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.198594606428488</v>
+        <v>-0.179259463160369</v>
       </c>
     </row>
     <row r="761">
@@ -9375,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.0313170160996901</v>
+        <v>-0.0369298740410628</v>
       </c>
     </row>
     <row r="762">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.154200617266077</v>
+        <v>-0.0845616665532447</v>
       </c>
     </row>
     <row r="763">
@@ -9397,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.429833027542911</v>
+        <v>-0.35454202673558</v>
       </c>
     </row>
     <row r="764">
@@ -9408,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.209411504195337</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="765">
@@ -9419,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.319974811147471</v>
+        <v>-0.439081068128802</v>
       </c>
     </row>
     <row r="766">
@@ -9430,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.720911578229036</v>
+        <v>-0.505976832317511</v>
       </c>
     </row>
     <row r="767">
@@ -9474,7 +9468,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.520816859010516</v>
+        <v>-0.302466085358302</v>
       </c>
     </row>
     <row r="771">
@@ -9485,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.334673612868341</v>
+        <v>-0.258139644682972</v>
       </c>
     </row>
     <row r="772">
@@ -9507,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-1.07352951331754</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="774">
@@ -9529,7 +9523,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.529924735096339</v>
       </c>
     </row>
     <row r="776">
@@ -9540,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.246681772745037</v>
+        <v>-0.23797128564372</v>
       </c>
     </row>
     <row r="777">
@@ -9551,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.382018275892245</v>
+        <v>-29.90220872798</v>
       </c>
     </row>
     <row r="778">
@@ -9562,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.159408478744795</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="779">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.398913566581877</v>
+        <v>-0.417942441380477</v>
       </c>
     </row>
     <row r="781">
@@ -9595,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.147959183673469</v>
+        <v>-10.022582724461</v>
       </c>
     </row>
     <row r="782">
@@ -9617,7 +9611,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.344306433615895</v>
+        <v>-0.32271443807213</v>
       </c>
     </row>
     <row r="784">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.155157969254498</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="785">
@@ -9639,7 +9633,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-1.46406013925347</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="786">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.231734962882869</v>
+        <v>-0.349336249095007</v>
       </c>
     </row>
     <row r="787">
@@ -9672,7 +9666,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-2.26821964672432</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="789">
@@ -9705,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.723991464962485</v>
+        <v>-0.631950462784037</v>
       </c>
     </row>
     <row r="792">
@@ -9716,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.446726348547341</v>
+        <v>-23.2235983113908</v>
       </c>
     </row>
     <row r="793">
@@ -9727,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>0.245528454501213</v>
+        <v>-0.490624308650264</v>
       </c>
     </row>
     <row r="794">
@@ -9738,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.270513344785146</v>
+        <v>-0.317342345105734</v>
       </c>
     </row>
     <row r="795">
@@ -9749,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.250054438917381</v>
+        <v>-0.212485964050949</v>
       </c>
     </row>
     <row r="796">
@@ -9760,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.36125529561184</v>
+        <v>-9.14387696952913</v>
       </c>
     </row>
     <row r="797">
@@ -9771,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.208313514860384</v>
+        <v>-0.181372225963267</v>
       </c>
     </row>
     <row r="798">
@@ -9782,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.254415156529114</v>
+        <v>-0.213696242827435</v>
       </c>
     </row>
     <row r="799">
@@ -9793,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.282074270480404</v>
+        <v>-0.615969207007149</v>
       </c>
     </row>
     <row r="800">
@@ -9804,7 +9798,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.542948082312732</v>
       </c>
     </row>
     <row r="801">
@@ -9815,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.14795918367347</v>
+        <v>-4.02027976011621</v>
       </c>
     </row>
     <row r="802">
@@ -9826,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.631692779316674</v>
+        <v>-3.82221280392648</v>
       </c>
     </row>
     <row r="803">
@@ -9837,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-8.27708231171854</v>
+        <v>-0.624685214537982</v>
       </c>
     </row>
     <row r="804">
@@ -9848,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.373472490091368</v>
       </c>
     </row>
     <row r="805">
@@ -9859,7 +9853,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.241472738985196</v>
+        <v>-0.203798004423715</v>
       </c>
     </row>
     <row r="806">
@@ -9870,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.18146445675372</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="807">
@@ -9881,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.53182705190068</v>
       </c>
     </row>
     <row r="808">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.58174111063351</v>
+        <v>-5.40057027029729</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.237611577949075</v>
+        <v>-0.252969682114829</v>
       </c>
     </row>
     <row r="810">
@@ -9925,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-32.9200119978737</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="812">
@@ -9936,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.467341038432435</v>
       </c>
     </row>
     <row r="813">
@@ -9947,7 +9941,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.359483100594062</v>
+        <v>-0.276265998912963</v>
       </c>
     </row>
     <row r="814">
@@ -9958,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.484969983224691</v>
+        <v>-0.440788122757243</v>
       </c>
     </row>
     <row r="815">
@@ -9969,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.330133470772145</v>
+        <v>-0.170524298373498</v>
       </c>
     </row>
     <row r="816">
@@ -9980,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.337908705965839</v>
+        <v>-0.051310023418488</v>
       </c>
     </row>
     <row r="817">
@@ -9991,7 +9985,7 @@
         <v>16</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.348518013049816</v>
+        <v>-0.228867924279447</v>
       </c>
     </row>
     <row r="818">
@@ -10002,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.36063946134266</v>
       </c>
     </row>
     <row r="819">
@@ -10013,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.292842973434972</v>
+        <v>-0.273030009570289</v>
       </c>
     </row>
     <row r="820">
@@ -10024,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.191765313481989</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="821">
@@ -10035,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.707537300034798</v>
+        <v>-0.231837451319647</v>
       </c>
     </row>
     <row r="822">
@@ -10068,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.316457477068925</v>
+        <v>-0.226488618552534</v>
       </c>
     </row>
     <row r="825">
@@ -10079,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.411543161579583</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="826">
@@ -10090,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>0.109009469553271</v>
+        <v>0.000622983714843595</v>
       </c>
     </row>
     <row r="827">
@@ -10112,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.167945614419075</v>
       </c>
     </row>
     <row r="829">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.0989475391089352</v>
+        <v>0.0161785704580591</v>
       </c>
     </row>
     <row r="830">
@@ -10134,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.207460347779119</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="831">
@@ -10145,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.158964679231146</v>
       </c>
     </row>
     <row r="832">
@@ -10156,7 +10150,7 @@
         <v>16</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.61591274773888</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="833">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.31023372963213</v>
+        <v>-0.359512095225817</v>
       </c>
     </row>
     <row r="834">
@@ -10178,7 +10172,7 @@
         <v>16</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.221388226458807</v>
+        <v>-0.209967366983622</v>
       </c>
     </row>
     <row r="835">
@@ -10189,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.281887941225745</v>
+        <v>-0.253600407530326</v>
       </c>
     </row>
     <row r="836">
@@ -10200,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.65058638201539</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="837">
@@ -10211,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.176115090324109</v>
+        <v>-0.313359996268376</v>
       </c>
     </row>
     <row r="838">
@@ -10222,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.962682102128596</v>
+        <v>-0.23137734552872</v>
       </c>
     </row>
     <row r="839">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.173323887752191</v>
       </c>
     </row>
     <row r="840">
@@ -10244,7 +10238,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.224921276919908</v>
+        <v>-0.201928996337605</v>
       </c>
     </row>
     <row r="841">
@@ -10266,7 +10260,7 @@
         <v>16</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.367405877451251</v>
+        <v>-0.589706026754177</v>
       </c>
     </row>
     <row r="843">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>0.403867553149862</v>
+        <v>-0.186821136648924</v>
       </c>
     </row>
     <row r="844">
@@ -10288,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.269572564011014</v>
+        <v>-2.44249603582472</v>
       </c>
     </row>
     <row r="845">
@@ -10299,7 +10293,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>0.0177121527594344</v>
+        <v>-0.38222204770635</v>
       </c>
     </row>
     <row r="846">
@@ -10310,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.194933516564585</v>
       </c>
     </row>
     <row r="847">
@@ -10321,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.606281240773392</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="848">
@@ -10332,7 +10326,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.170463312244813</v>
+        <v>-0.283694248226878</v>
       </c>
     </row>
     <row r="849">
@@ -10343,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.168763542190914</v>
       </c>
     </row>
     <row r="850">
@@ -10354,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.448699852860274</v>
+        <v>-0.405261900553274</v>
       </c>
     </row>
     <row r="851">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.36655618765385</v>
+        <v>-0.236169020728958</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-2.75997709964179</v>
+        <v>-2.0050630998679</v>
       </c>
     </row>
     <row r="853">
@@ -10387,7 +10381,7 @@
         <v>16</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.160946290103039</v>
+        <v>-1.29686929106755</v>
       </c>
     </row>
     <row r="854">
@@ -10398,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.2029774707926</v>
       </c>
     </row>
     <row r="855">
@@ -10420,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.251094448428173</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="857">
@@ -10431,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.144838916991437</v>
+        <v>-0.195089871131747</v>
       </c>
     </row>
     <row r="858">
@@ -10442,7 +10436,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.300383144356499</v>
+        <v>-0.157191021491588</v>
       </c>
     </row>
     <row r="859">
@@ -10464,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.366011341562266</v>
+        <v>-0.33846251030687</v>
       </c>
     </row>
     <row r="861">
@@ -10475,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-16.6039165544157</v>
+        <v>-1.44405808373394</v>
       </c>
     </row>
     <row r="862">
@@ -10486,7 +10480,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.286367214843826</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="863">
@@ -10508,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.86498247992227</v>
       </c>
     </row>
     <row r="865">
@@ -10519,7 +10513,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.437873989899378</v>
+        <v>-0.415295915256809</v>
       </c>
     </row>
     <row r="866">
@@ -10530,7 +10524,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.370020679311602</v>
+        <v>-0.333952285295213</v>
       </c>
     </row>
     <row r="867">
@@ -10541,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.506035396853713</v>
+        <v>-0.240546213810857</v>
       </c>
     </row>
     <row r="868">
@@ -10552,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-3.57433920871293</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="869">
@@ -10563,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.543597767360155</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="870">
@@ -10574,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>0.173568134719601</v>
+        <v>0.362287607045662</v>
       </c>
     </row>
     <row r="871">
@@ -10585,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.160173130289831</v>
+        <v>-0.188170540252257</v>
       </c>
     </row>
     <row r="872">
@@ -10596,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.277108386579604</v>
+        <v>-0.184347421004091</v>
       </c>
     </row>
     <row r="873">
@@ -10618,7 +10612,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.320622608725659</v>
       </c>
     </row>
     <row r="875">
@@ -10629,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.271663938747463</v>
+        <v>-0.830391996925559</v>
       </c>
     </row>
     <row r="876">
@@ -10640,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.263622288094931</v>
+        <v>-0.188533703361003</v>
       </c>
     </row>
     <row r="877">
@@ -10651,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.753231405948649</v>
       </c>
     </row>
     <row r="878">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.224204324917011</v>
+        <v>-0.233716487607678</v>
       </c>
     </row>
     <row r="881">
@@ -10695,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>0.125104568789794</v>
+        <v>-1.69844417377351</v>
       </c>
     </row>
     <row r="882">
@@ -10706,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.545176257781723</v>
+        <v>-0.653486093101627</v>
       </c>
     </row>
     <row r="883">
@@ -10717,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>0.0552326444787044</v>
+        <v>0.263199011133883</v>
       </c>
     </row>
     <row r="884">
@@ -10739,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.924935839096082</v>
+        <v>-1.07793545799538</v>
       </c>
     </row>
     <row r="886">
@@ -10750,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-1.13093936307907</v>
+        <v>-0.361775688985966</v>
       </c>
     </row>
     <row r="887">
@@ -10761,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.558441491200517</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="888">
@@ -10772,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.252151119641927</v>
       </c>
     </row>
     <row r="889">
@@ -10783,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.650010902939257</v>
+        <v>-0.537284097592796</v>
       </c>
     </row>
     <row r="890">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.636864322053974</v>
+        <v>-0.271824688097919</v>
       </c>
     </row>
     <row r="892">
@@ -10816,7 +10810,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.693895003215708</v>
       </c>
     </row>
     <row r="893">
@@ -10827,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-1.0978333677115</v>
+        <v>-58.1595022456804</v>
       </c>
     </row>
     <row r="894">
@@ -10838,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-2.09620145766504</v>
+        <v>-2.00749687683669</v>
       </c>
     </row>
     <row r="895">
@@ -10849,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.287250246246962</v>
+        <v>-0.429395058741663</v>
       </c>
     </row>
     <row r="896">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.205181886328275</v>
+        <v>-0.236730702827096</v>
       </c>
     </row>
     <row r="897">
@@ -10871,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.373684660981282</v>
+        <v>-77.8647312334888</v>
       </c>
     </row>
     <row r="898">
@@ -10893,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.211795605161245</v>
       </c>
     </row>
     <row r="900">
@@ -10904,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.243410799522139</v>
       </c>
     </row>
     <row r="901">
@@ -10915,7 +10909,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.496637644787293</v>
+        <v>-0.731410427612747</v>
       </c>
     </row>
     <row r="902">
@@ -10926,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.891790929040204</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="903">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.30933423437486</v>
+        <v>-0.213605301016365</v>
       </c>
     </row>
     <row r="905">
@@ -10959,7 +10953,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.222464188093086</v>
+        <v>-0.324578533920624</v>
       </c>
     </row>
     <row r="906">
@@ -10981,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.148478365953361</v>
+        <v>-0.204849182850738</v>
       </c>
     </row>
     <row r="908">
@@ -10992,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-3.01377441281485</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="909">
@@ -11003,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.212376849045361</v>
+        <v>-0.290527738682697</v>
       </c>
     </row>
     <row r="910">
@@ -11014,7 +11008,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.284229139523621</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="911">
@@ -11025,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.19610987068758</v>
+        <v>-0.202014368139539</v>
       </c>
     </row>
     <row r="912">
@@ -11036,7 +11030,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.50330892639698</v>
       </c>
     </row>
     <row r="913">
@@ -11080,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.188977515499172</v>
       </c>
     </row>
     <row r="917">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.50278103670136</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="918">
@@ -11102,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.294382118672816</v>
+        <v>-0.321900719238955</v>
       </c>
     </row>
     <row r="919">
@@ -11124,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.127218711597884</v>
+        <v>-0.211544918241596</v>
       </c>
     </row>
     <row r="921">
@@ -11146,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.545671642256299</v>
+        <v>-0.1994779111543</v>
       </c>
     </row>
     <row r="923">
@@ -11157,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.528747680503729</v>
+        <v>-0.0697748348335994</v>
       </c>
     </row>
     <row r="924">
@@ -11168,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.396831151772645</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="925">
@@ -11179,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-1.33367948711917</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="926">
@@ -11190,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.559366812009671</v>
+        <v>-0.192800151054932</v>
       </c>
     </row>
     <row r="927">
@@ -11201,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.217330396359949</v>
+        <v>-0.262854311656866</v>
       </c>
     </row>
     <row r="928">
@@ -11223,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.251330859703383</v>
+        <v>-0.750435749846836</v>
       </c>
     </row>
     <row r="930">
@@ -11245,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.163934477915299</v>
+        <v>-0.712037382186983</v>
       </c>
     </row>
     <row r="932">
@@ -11267,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.334540045953146</v>
+        <v>-0.673858451803671</v>
       </c>
     </row>
     <row r="934">
@@ -11278,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.419369392454091</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="935">
@@ -11289,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>0.500099849021897</v>
+        <v>0.535227463289136</v>
       </c>
     </row>
     <row r="936">
@@ -11311,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.208918127400501</v>
+        <v>-0.14488524780742</v>
       </c>
     </row>
     <row r="938">
@@ -11322,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.311225153986665</v>
+        <v>-0.698503377794402</v>
       </c>
     </row>
     <row r="939">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.026742918470672</v>
+        <v>-0.200451764447397</v>
       </c>
     </row>
     <row r="941">
@@ -11355,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.1634267988742</v>
+        <v>-0.671855360981873</v>
       </c>
     </row>
     <row r="942">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.854653765699828</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="943">
@@ -11377,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.610142916775484</v>
+        <v>-0.234383482405554</v>
       </c>
     </row>
     <row r="944">
@@ -11399,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.218834981364919</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="946">
@@ -11410,7 +11404,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.193790936504366</v>
+        <v>-0.569768877811996</v>
       </c>
     </row>
     <row r="947">
@@ -11421,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.906942427248454</v>
+        <v>-0.270833464414349</v>
       </c>
     </row>
     <row r="948">
@@ -11432,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.760644101046424</v>
+        <v>-0.178025437456419</v>
       </c>
     </row>
     <row r="949">
@@ -11454,7 +11448,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.37523011882636</v>
       </c>
     </row>
     <row r="951">
@@ -11487,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.378664708053214</v>
+        <v>-0.588193133758939</v>
       </c>
     </row>
     <row r="954">
@@ -11498,7 +11492,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.78744437741721</v>
       </c>
     </row>
     <row r="955">
@@ -11509,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.224614276030726</v>
       </c>
     </row>
     <row r="956">
@@ -11520,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.287008451987968</v>
+        <v>-0.2458311533483</v>
       </c>
     </row>
     <row r="957">
@@ -11531,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-1.13207911061219</v>
+        <v>-0.190247434319306</v>
       </c>
     </row>
     <row r="958">
@@ -11553,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.746139481450601</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="960">
@@ -11586,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.39274097485554</v>
+        <v>-0.341367552878495</v>
       </c>
     </row>
     <row r="963">
@@ -11597,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.617026207402417</v>
+        <v>-0.334918206697713</v>
       </c>
     </row>
     <row r="964">
@@ -11608,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.129244807914692</v>
+        <v>-0.102561284988215</v>
       </c>
     </row>
     <row r="965">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.215220485576045</v>
+        <v>-0.208841317289775</v>
       </c>
     </row>
     <row r="966">
@@ -11630,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.375429369620926</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="967">
@@ -11641,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.126856313168912</v>
+        <v>0.0660952324453171</v>
       </c>
     </row>
     <row r="968">
@@ -11663,7 +11657,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.27661725763448</v>
       </c>
     </row>
     <row r="970">
@@ -11707,7 +11701,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.476265461765297</v>
+        <v>0.207647791550642</v>
       </c>
     </row>
     <row r="974">
@@ -11729,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.185665408623873</v>
+        <v>0.143800679628978</v>
       </c>
     </row>
     <row r="976">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.521201383932116</v>
+        <v>-0.161908700708198</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.278416991820519</v>
+        <v>-0.146284696164054</v>
       </c>
     </row>
     <row r="979">
@@ -11773,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.78332379487472</v>
+        <v>0.0981777691589626</v>
       </c>
     </row>
     <row r="980">
@@ -11806,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.583258529591368</v>
+        <v>-0.437157340491253</v>
       </c>
     </row>
     <row r="983">
@@ -11817,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-1.13103119421411</v>
+        <v>-8.95361341142414</v>
       </c>
     </row>
     <row r="984">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>0.107700330113372</v>
+        <v>-0.338883425257653</v>
       </c>
     </row>
     <row r="986">
@@ -11861,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.202544208637532</v>
+        <v>-0.931256868203563</v>
       </c>
     </row>
     <row r="988">
@@ -11883,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.491601255250085</v>
+        <v>-0.293350736507954</v>
       </c>
     </row>
     <row r="990">
@@ -11916,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.310237735550994</v>
+        <v>-0.697874515747199</v>
       </c>
     </row>
     <row r="993">
@@ -11927,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.335410112957889</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="994">
@@ -11949,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.18642706458428</v>
       </c>
     </row>
     <row r="996">
@@ -11960,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-5.1706764622646</v>
+        <v>-0.67222730965277</v>
       </c>
     </row>
     <row r="997">
@@ -11982,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.0430263661006896</v>
+        <v>0.018142663445832</v>
       </c>
     </row>
     <row r="999">
@@ -11993,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.156249729822401</v>
+        <v>-0.999218268098448</v>
       </c>
     </row>
     <row r="1000">
@@ -12004,7 +11998,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>0.451803903057771</v>
+        <v>-0.00601609368027667</v>
       </c>
     </row>
     <row r="1001">
@@ -12015,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.258026945063822</v>
+        <v>-1.28969946606012</v>
       </c>
     </row>
     <row r="1002">
@@ -12026,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.696000029379487</v>
+        <v>-24.1779664647508</v>
       </c>
     </row>
     <row r="1003">
@@ -12048,7 +12042,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.303162728544396</v>
+        <v>-0.772109225139846</v>
       </c>
     </row>
     <row r="1005">
@@ -12059,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>0.0653123890117209</v>
+        <v>-0.367517867157042</v>
       </c>
     </row>
     <row r="1006">
@@ -12070,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>0.174147414789961</v>
+        <v>-0.0323371846708553</v>
       </c>
     </row>
     <row r="1007">
@@ -12081,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.612379546948221</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1008">
@@ -12092,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>0.0606629580538249</v>
+        <v>0.241579592558217</v>
       </c>
     </row>
     <row r="1009">
@@ -12103,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.179432522178713</v>
       </c>
     </row>
     <row r="1010">
@@ -12114,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.0481935374780585</v>
+        <v>-0.306297757100458</v>
       </c>
     </row>
     <row r="1011">
@@ -12136,7 +12130,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.499168639045054</v>
+        <v>-0.644875575508314</v>
       </c>
     </row>
     <row r="1013">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.198875589729492</v>
+        <v>-0.153761977836613</v>
       </c>
     </row>
     <row r="1014">
@@ -12169,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.302108837977974</v>
+        <v>-0.163020258056857</v>
       </c>
     </row>
     <row r="1016">
@@ -12180,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.181954045206823</v>
+        <v>-0.195061824952704</v>
       </c>
     </row>
     <row r="1017">
@@ -12191,7 +12185,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-1.01625964721603</v>
+        <v>-0.303620477649696</v>
       </c>
     </row>
     <row r="1018">
@@ -12213,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.0443776177871573</v>
+        <v>0.171010526789374</v>
       </c>
     </row>
     <row r="1020">
@@ -12224,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.539865854937595</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1021">
@@ -12246,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.176980105413692</v>
+        <v>-10.3833856512269</v>
       </c>
     </row>
     <row r="1023">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.101790774467415</v>
+        <v>-0.174776887648482</v>
       </c>
     </row>
     <row r="1024">
@@ -12279,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.320690296331747</v>
+        <v>-0.674645743697415</v>
       </c>
     </row>
     <row r="1026">
@@ -12301,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-1.43863096342986</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1028">
@@ -12312,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.315170350777956</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1029">
@@ -12323,7 +12317,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.322760249556366</v>
+        <v>-0.178141170369403</v>
       </c>
     </row>
     <row r="1030">
@@ -12334,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.200666294109298</v>
+        <v>-0.206814238370289</v>
       </c>
     </row>
     <row r="1031">
@@ -12345,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.36429705319023</v>
+        <v>-0.0258677022973266</v>
       </c>
     </row>
     <row r="1032">
@@ -12367,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.192383256929654</v>
+        <v>-0.193676835761506</v>
       </c>
     </row>
     <row r="1034">
@@ -12378,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.376848447043947</v>
+        <v>-0.521994434386057</v>
       </c>
     </row>
     <row r="1035">
@@ -12389,7 +12383,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.506794687047411</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1036">
@@ -12411,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.438162673145283</v>
+        <v>0.318402219754845</v>
       </c>
     </row>
     <row r="1038">
@@ -12422,7 +12416,7 @@
         <v>16</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.479831977028945</v>
+        <v>-0.9450746383238</v>
       </c>
     </row>
     <row r="1039">
@@ -12444,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.293155572256574</v>
+        <v>-0.220506656208421</v>
       </c>
     </row>
     <row r="1041">
@@ -12455,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.176386632738667</v>
+        <v>-0.19559283822856</v>
       </c>
     </row>
     <row r="1042">
@@ -12477,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.443821490808145</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1044">
@@ -12488,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>0.122684889048317</v>
+        <v>-0.178677846340601</v>
       </c>
     </row>
     <row r="1045">
@@ -12499,7 +12493,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-2.1810907911009</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1046">
@@ -12510,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.304386246551801</v>
+        <v>-0.373231828994388</v>
       </c>
     </row>
     <row r="1047">
@@ -12532,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.368142675483365</v>
+        <v>0.784385864776108</v>
       </c>
     </row>
     <row r="1049">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.413362280034791</v>
+        <v>-0.260887349842216</v>
       </c>
     </row>
     <row r="1051">
@@ -12565,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.145118149807127</v>
+        <v>-0.263731414596545</v>
       </c>
     </row>
     <row r="1052">
@@ -12576,7 +12570,7 @@
         <v>16</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.449029086561013</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1053">
@@ -12598,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.15945334062108</v>
+        <v>-0.23332114125971</v>
       </c>
     </row>
     <row r="1055">
@@ -12609,7 +12603,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.154079578066999</v>
+        <v>-0.413487503218857</v>
       </c>
     </row>
     <row r="1056">
@@ -12642,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.198991937940887</v>
       </c>
     </row>
     <row r="1059">
@@ -12653,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.613767887849505</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1060">
@@ -12664,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.0544632497774387</v>
+        <v>-0.0993976986900416</v>
       </c>
     </row>
     <row r="1061">
@@ -12675,7 +12669,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.159763313609468</v>
+        <v>-102.369328921938</v>
       </c>
     </row>
     <row r="1062">
@@ -12686,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.616889136700505</v>
       </c>
     </row>
     <row r="1063">
@@ -12697,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.500607429421029</v>
+        <v>-1.47139509532693</v>
       </c>
     </row>
     <row r="1064">
@@ -12708,7 +12702,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.359692441053865</v>
+        <v>-0.157102783254451</v>
       </c>
     </row>
     <row r="1065">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.0564520296666655</v>
+        <v>-2.23027298243868</v>
       </c>
     </row>
     <row r="1067">
@@ -12752,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.116091110518083</v>
+        <v>-0.952941784160382</v>
       </c>
     </row>
     <row r="1069">
@@ -12763,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.378402115737928</v>
+        <v>-0.169183894834467</v>
       </c>
     </row>
     <row r="1070">
@@ -12774,7 +12768,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.196743228371475</v>
+        <v>0.138558285288493</v>
       </c>
     </row>
     <row r="1071">
@@ -12785,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.165075999139877</v>
       </c>
     </row>
     <row r="1072">
@@ -12796,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.18939210098347</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1073">
@@ -12807,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.159763313609467</v>
+        <v>-36.8924459374709</v>
       </c>
     </row>
     <row r="1074">
@@ -12818,7 +12812,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.0694843782252</v>
       </c>
     </row>
     <row r="1075">
@@ -12829,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.250774224202885</v>
+        <v>-0.292535572031816</v>
       </c>
     </row>
     <row r="1076">
@@ -12840,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.165200634937054</v>
       </c>
     </row>
     <row r="1077">
@@ -12862,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.220844427341239</v>
+        <v>-0.949437253357878</v>
       </c>
     </row>
     <row r="1079">
@@ -12873,7 +12867,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.983370310764805</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1080">
@@ -12884,7 +12878,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.242620963008731</v>
+        <v>-0.292239220379607</v>
       </c>
     </row>
     <row r="1081">
@@ -12895,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.0590630417558512</v>
+        <v>0.101478479938304</v>
       </c>
     </row>
     <row r="1082">
@@ -12928,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.492036968389115</v>
       </c>
     </row>
     <row r="1085">
@@ -12939,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.202320899273589</v>
       </c>
     </row>
     <row r="1086">
@@ -12983,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.336609649469673</v>
+        <v>0.252220239468768</v>
       </c>
     </row>
     <row r="1090">
@@ -13005,7 +12999,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.0270610964520599</v>
+        <v>0.172611961358067</v>
       </c>
     </row>
     <row r="1092">
@@ -13016,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.419983195598483</v>
       </c>
     </row>
     <row r="1093">
@@ -13027,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.184310179266152</v>
+        <v>-0.197596015730047</v>
       </c>
     </row>
     <row r="1094">
@@ -13038,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.175726124854852</v>
+        <v>-1.56197375071471</v>
       </c>
     </row>
     <row r="1095">
@@ -13049,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.126070026044265</v>
+        <v>-49.382048436494</v>
       </c>
     </row>
     <row r="1096">
@@ -13060,7 +13054,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.347485918081526</v>
       </c>
     </row>
     <row r="1097">
@@ -13071,7 +13065,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.159763313609468</v>
+        <v>-3.74167587390258</v>
       </c>
     </row>
     <row r="1098">
@@ -13082,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.159763313609468</v>
+        <v>-20.9197375836825</v>
       </c>
     </row>
     <row r="1099">
@@ -13093,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.146601763232935</v>
+        <v>-0.392972569272256</v>
       </c>
     </row>
     <row r="1100">
@@ -13104,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.133429596751813</v>
+        <v>-1.15209777757872</v>
       </c>
     </row>
     <row r="1101">
@@ -13115,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.668908406747852</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1102">
@@ -13137,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.841702446182019</v>
       </c>
     </row>
     <row r="1104">
@@ -13148,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.0260215457966577</v>
+        <v>-0.216605164431048</v>
       </c>
     </row>
     <row r="1105">
@@ -13159,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.518730458405946</v>
       </c>
     </row>
     <row r="1106">
@@ -13170,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.195766836743575</v>
+        <v>-0.0636159489992569</v>
       </c>
     </row>
     <row r="1107">
@@ -13181,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.539298204048381</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1108">
@@ -13203,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-39.3370927494642</v>
       </c>
     </row>
     <row r="1110">
@@ -13214,7 +13208,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.41327740646608</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1111">
@@ -13225,7 +13219,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-2.39653626377749</v>
+        <v>-0.366783266107044</v>
       </c>
     </row>
     <row r="1112">
@@ -13247,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.628736322740412</v>
       </c>
     </row>
     <row r="1114">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.41951126412796</v>
+        <v>-0.405384621875412</v>
       </c>
     </row>
     <row r="1116">
@@ -13280,7 +13274,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.228561755349495</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1117">
@@ -13313,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.111797110950466</v>
+        <v>-0.194984754788333</v>
       </c>
     </row>
     <row r="1120">
@@ -13324,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.124409301399857</v>
+        <v>0.0766650838946719</v>
       </c>
     </row>
     <row r="1121">
@@ -13335,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.280237429977627</v>
+        <v>-0.154699338606614</v>
       </c>
     </row>
     <row r="1122">
@@ -13379,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.529996567239716</v>
+        <v>-0.26293604340717</v>
       </c>
     </row>
     <row r="1126">
@@ -13412,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.784927366464149</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1129">
@@ -13434,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.0249190375630268</v>
+        <v>-97.3169604771816</v>
       </c>
     </row>
     <row r="1131">
@@ -13445,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.608616319867556</v>
+        <v>-0.666338442834595</v>
       </c>
     </row>
     <row r="1132">
@@ -13456,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.57165478752232</v>
       </c>
     </row>
     <row r="1133">
@@ -13467,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.670762160451051</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1134">
@@ -13500,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.317224410665101</v>
+        <v>-0.212398653944566</v>
       </c>
     </row>
     <row r="1137">
@@ -13522,7 +13516,7 @@
         <v>16</v>
       </c>
       <c r="C1138" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.180325125885152</v>
       </c>
     </row>
     <row r="1139">
@@ -13533,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.187415040621083</v>
+        <v>-0.700022739302984</v>
       </c>
     </row>
     <row r="1140">
@@ -13555,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.244329175296169</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1142">
@@ -13566,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.184708265480924</v>
+        <v>-2.14467652778527</v>
       </c>
     </row>
     <row r="1143">
@@ -13577,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.164162412747859</v>
       </c>
     </row>
     <row r="1144">
@@ -13588,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.224609989797744</v>
       </c>
     </row>
     <row r="1145">
@@ -13599,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.30108002809655</v>
       </c>
     </row>
     <row r="1146">
@@ -13621,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.180601882845017</v>
+        <v>-0.225891047212741</v>
       </c>
     </row>
     <row r="1148">
@@ -13643,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.209070384175659</v>
       </c>
     </row>
     <row r="1150">
@@ -13687,7 +13681,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.98599201484303</v>
       </c>
     </row>
     <row r="1154">
@@ -13698,7 +13692,7 @@
         <v>16</v>
       </c>
       <c r="C1154" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.461705126672555</v>
       </c>
     </row>
     <row r="1155">
@@ -13720,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.177245095732914</v>
       </c>
     </row>
     <row r="1157">
@@ -13742,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.568282929026162</v>
+        <v>-0.653459860013471</v>
       </c>
     </row>
     <row r="1159">
@@ -13764,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.0128099629483307</v>
+        <v>-0.216447559882669</v>
       </c>
     </row>
     <row r="1161">
@@ -13797,7 +13791,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.600028950136569</v>
+        <v>-0.213628132186264</v>
       </c>
     </row>
     <row r="1164">
@@ -13819,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.853830756724202</v>
+        <v>-6.96353000211432</v>
       </c>
     </row>
     <row r="1166">
@@ -13830,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.374069985198836</v>
       </c>
     </row>
     <row r="1167">
@@ -13841,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.0704843210481993</v>
+        <v>-0.156116703027677</v>
       </c>
     </row>
     <row r="1168">
@@ -13863,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.41184930217264</v>
       </c>
     </row>
     <row r="1170">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-1.75094150782004</v>
+        <v>-7.18585946967531</v>
       </c>
     </row>
     <row r="1171">
@@ -13885,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.770164468465315</v>
       </c>
     </row>
     <row r="1172">
@@ -13896,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.889902807045528</v>
       </c>
     </row>
     <row r="1173">
@@ -13907,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.288545842397103</v>
+        <v>-0.256105340627488</v>
       </c>
     </row>
     <row r="1174">
@@ -13918,7 +13912,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>-0.834814393501312</v>
+        <v>-0.512436862697089</v>
       </c>
     </row>
     <row r="1175">
@@ -13929,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.00958157167467444</v>
+        <v>-0.104274731471709</v>
       </c>
     </row>
     <row r="1176">
@@ -13940,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-1.33675846606729</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1177">
@@ -13984,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-1.60234658115941</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1181">
@@ -13995,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.17461424323881</v>
+        <v>-0.244362029537569</v>
       </c>
     </row>
     <row r="1182">
@@ -14006,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.48540346149181</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1183">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-1.89431279159623</v>
+        <v>-0.213129715466186</v>
       </c>
     </row>
     <row r="1185">
@@ -14050,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.158563403738209</v>
+        <v>-0.184572528479937</v>
       </c>
     </row>
     <row r="1187">
@@ -14061,7 +14055,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.225695272923001</v>
+        <v>-17.3382293357289</v>
       </c>
     </row>
     <row r="1188">
@@ -14072,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.159763313609467</v>
+        <v>-13.7358541046331</v>
       </c>
     </row>
     <row r="1189">
@@ -14083,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.433967688521512</v>
+        <v>-0.294283408223158</v>
       </c>
     </row>
     <row r="1190">
@@ -14094,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-1.58552134382558</v>
+        <v>-1.53578090393902</v>
       </c>
     </row>
     <row r="1191">
@@ -14127,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.661275362346029</v>
+        <v>-1.45331958906544</v>
       </c>
     </row>
     <row r="1194">
@@ -14138,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.193894306768742</v>
+        <v>-0.165034686342299</v>
       </c>
     </row>
     <row r="1195">
@@ -14149,7 +14143,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.294155622114352</v>
+        <v>-0.241525076035604</v>
       </c>
     </row>
     <row r="1196">
@@ -14160,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.442655327802438</v>
+        <v>-0.671702905243727</v>
       </c>
     </row>
     <row r="1197">
@@ -14171,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.664504642245782</v>
+        <v>-0.503007269770672</v>
       </c>
     </row>
     <row r="1198">
@@ -14182,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.13560046857719</v>
+        <v>0.120141992960165</v>
       </c>
     </row>
     <row r="1199">
@@ -14193,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.201847936684484</v>
+        <v>-0.201591309624274</v>
       </c>
     </row>
     <row r="1200">
@@ -14204,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.199049931566149</v>
+        <v>-0.360382168714089</v>
       </c>
     </row>
     <row r="1201">
@@ -14215,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.176848222609377</v>
+        <v>-0.16059052006702</v>
       </c>
     </row>
   </sheetData>
@@ -14294,7 +14288,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>4.23357142857143</v>
+        <v>3.4048056596002</v>
       </c>
     </row>
     <row r="5">
@@ -14328,7 +14322,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>23.4823119227499</v>
+        <v>29.4334670948413</v>
       </c>
     </row>
     <row r="7">
@@ -14362,7 +14356,7 @@
         <v>8.06</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0593794381160786</v>
+        <v>1.69127281452687</v>
       </c>
     </row>
     <row r="9">
@@ -14379,7 +14373,7 @@
         <v>0.79</v>
       </c>
       <c r="E9" t="n">
-        <v>5.155</v>
+        <v>5.07489163840198</v>
       </c>
     </row>
     <row r="10">
@@ -14396,7 +14390,7 @@
         <v>0.85</v>
       </c>
       <c r="E10" t="n">
-        <v>5.15071428571428</v>
+        <v>5.16004929210992</v>
       </c>
     </row>
     <row r="11">
@@ -14447,7 +14441,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>8.56927481968452</v>
+        <v>7.60013435431544</v>
       </c>
     </row>
     <row r="14">
@@ -14464,7 +14458,7 @@
         <v>-6.6</v>
       </c>
       <c r="E14" t="n">
-        <v>5.45534314100006</v>
+        <v>5.38598813440831</v>
       </c>
     </row>
     <row r="15">
@@ -14566,7 +14560,7 @@
         <v>274.62</v>
       </c>
       <c r="E20" t="n">
-        <v>-2653.37457084582</v>
+        <v>-3125.82907346713</v>
       </c>
     </row>
     <row r="21">
@@ -14702,7 +14696,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E28" t="n">
-        <v>225.16204378082</v>
+        <v>226.983892998576</v>
       </c>
     </row>
     <row r="29">
@@ -14736,7 +14730,7 @@
         <v>-2594.04</v>
       </c>
       <c r="E30" t="n">
-        <v>-25.7157142857143</v>
+        <v>41.0706085963023</v>
       </c>
     </row>
     <row r="31">
@@ -14821,7 +14815,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-17.435</v>
+        <v>-3774.6216581652</v>
       </c>
     </row>
     <row r="36">
@@ -14957,7 +14951,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E43" t="n">
-        <v>296.442419593871</v>
+        <v>251.003690615702</v>
       </c>
     </row>
     <row r="44">
@@ -15093,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>4.29610810933103</v>
+        <v>4.23807921165297</v>
       </c>
     </row>
     <row r="52">
@@ -15127,7 +15121,7 @@
         <v>3.879</v>
       </c>
       <c r="E53" t="n">
-        <v>1.29021691125895</v>
+        <v>1.25171567772537</v>
       </c>
     </row>
     <row r="54">
@@ -15229,7 +15223,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>2.14569020521185</v>
+        <v>2.10257142857143</v>
       </c>
     </row>
     <row r="60">
@@ -15798,10 +15792,10 @@
         <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.266666666666667</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -15815,10 +15809,10 @@
         <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.266666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -15832,10 +15826,10 @@
         <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5">
@@ -15849,10 +15843,10 @@
         <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -15874,19 +15868,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -15897,7 +15891,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -15914,13 +15908,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -15931,13 +15925,13 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -15948,13 +15942,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -15965,7 +15959,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -15982,7 +15976,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -15999,7 +15993,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -16016,7 +16010,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -16033,7 +16027,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -16061,30 +16055,30 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -16095,13 +16089,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -16118,7 +16112,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -16129,69 +16123,188 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>
